--- a/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>15</v>
+        <v>999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3756,11 +3756,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3981,13 +3981,283 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>999</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>999</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>999</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>999</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>15</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>999</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>20</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>999</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>999</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>999</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
@@ -3128,22 +3128,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3231,22 +3231,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -3334,22 +3334,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3436,22 +3436,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3504,22 +3504,22 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3912,22 +3912,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3980,22 +3980,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4048,22 +4048,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4252,22 +4252,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4320,22 +4320,22 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4388,22 +4388,22 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4456,22 +4456,22 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4524,22 +4524,22 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4592,22 +4592,22 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4660,22 +4660,22 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4728,22 +4728,22 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4796,22 +4796,22 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4864,22 +4864,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">

--- a/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00027_2250_하나로H종신보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2716,22 +2716,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A02</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2819,22 +2819,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A03</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250003</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2922,22 +2922,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A04</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2975,11 +2975,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3025,22 +3025,22 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2250A01</t>
+          <t>2250A05</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2250001</t>
+          <t>2250005</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3128,22 +3128,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2250A02</t>
+          <t>2250A06</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2250002</t>
+          <t>2250006</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3229,72 +3229,20 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2250A02</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2250002</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
@@ -3332,72 +3280,20 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2250A02</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2250002</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
@@ -3433,1502 +3329,6 @@
       <c r="AV14" s="6" t="n"/>
       <c r="AW14" s="6" t="n"/>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2250A02</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2250002</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>999</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>999</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2250A02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2250002</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>999</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2250A03</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2250003</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>999</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2250A03</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2250003</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>999</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>15</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2250A03</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2250003</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>999</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>20</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2250A03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2250003</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>999</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>999</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2250A03</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2250003</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>999</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2250A04</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2250004</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>999</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2250A04</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2250004</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>999</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>15</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2250A04</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2250004</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>999</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>20</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2250A04</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2250004</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>999</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>999</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2250A04</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2250004</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>999</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2250A05</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2250005</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>999</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>10</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2250A05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2250005</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>999</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>15</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2250A05</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2250005</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>999</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>20</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2250A05</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2250005</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>999</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>999</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2250A05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2250005</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>999</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2250A06</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2250006</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>999</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>10</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2250A06</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2250006</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>999</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>15</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2250A06</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2250006</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>999</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>20</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2250A06</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2250006</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>999</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>999</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2250A06</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2250006</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>999</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="I3:N3"/>
